--- a/ig/document/StructureDefinition-medcom-contained-documentreference.xlsx
+++ b/ig/document/StructureDefinition-medcom-contained-documentreference.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-14T10:37:57+00:00</t>
+    <t>2026-03-10T10:54:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3218,7 +3218,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="3" hidden="true">
+    <row r="3">
       <c r="A3" t="s" s="2">
         <v>93</v>
       </c>
@@ -4726,7 +4726,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
         <v>179</v>
       </c>
@@ -5102,7 +5102,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
         <v>189</v>
       </c>
@@ -5226,7 +5226,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
         <v>197</v>
       </c>
@@ -5600,7 +5600,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
         <v>215</v>
       </c>
@@ -5726,7 +5726,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
         <v>219</v>
       </c>
@@ -6100,7 +6100,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
         <v>228</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
         <v>242</v>
       </c>
@@ -6722,7 +6722,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
         <v>249</v>
       </c>
@@ -6976,7 +6976,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>266</v>
       </c>
@@ -7480,7 +7480,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>294</v>
       </c>
@@ -8114,7 +8114,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" hidden="true">
+    <row r="42">
       <c r="A42" t="s" s="2">
         <v>329</v>
       </c>
@@ -8242,7 +8242,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="43" hidden="true">
+    <row r="43">
       <c r="A43" t="s" s="2">
         <v>338</v>
       </c>
@@ -8740,7 +8740,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
         <v>369</v>
       </c>
@@ -9372,7 +9372,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>382</v>
       </c>
@@ -9500,7 +9500,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
         <v>385</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
         <v>392</v>
       </c>
@@ -10126,7 +10126,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="58" hidden="true">
+    <row r="58">
       <c r="A58" t="s" s="2">
         <v>411</v>
       </c>
@@ -10500,7 +10500,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="61" hidden="true">
+    <row r="61">
       <c r="A61" t="s" s="2">
         <v>425</v>
       </c>
@@ -10878,7 +10878,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>435</v>
       </c>
@@ -11132,7 +11132,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>437</v>
       </c>
@@ -11258,7 +11258,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>438</v>
       </c>
@@ -11640,7 +11640,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="70" hidden="true">
+    <row r="70">
       <c r="A70" t="s" s="2">
         <v>448</v>
       </c>
@@ -12392,7 +12392,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="76" hidden="true">
+    <row r="76">
       <c r="A76" t="s" s="2">
         <v>464</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" hidden="true">
+    <row r="78">
       <c r="A78" t="s" s="2">
         <v>466</v>
       </c>
@@ -12772,7 +12772,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="79" hidden="true">
+    <row r="79">
       <c r="A79" t="s" s="2">
         <v>467</v>
       </c>
@@ -13154,7 +13154,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>470</v>
       </c>
@@ -13278,7 +13278,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>481</v>
       </c>
@@ -13528,7 +13528,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="85" hidden="true">
+    <row r="85">
       <c r="A85" t="s" s="2">
         <v>503</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
         <v>507</v>
       </c>
@@ -13908,7 +13908,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" hidden="true">
+    <row r="88">
       <c r="A88" t="s" s="2">
         <v>525</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="95" hidden="true">
+    <row r="95">
       <c r="A95" t="s" s="2">
         <v>567</v>
       </c>
@@ -15168,7 +15168,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
         <v>579</v>
       </c>
@@ -15546,7 +15546,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>582</v>
       </c>
@@ -15800,7 +15800,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>584</v>
       </c>
@@ -16308,7 +16308,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>588</v>
       </c>
@@ -16810,7 +16810,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="111" hidden="true">
+    <row r="111">
       <c r="A111" t="s" s="2">
         <v>596</v>
       </c>
@@ -17184,7 +17184,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="114" hidden="true">
+    <row r="114">
       <c r="A114" t="s" s="2">
         <v>606</v>
       </c>
@@ -17308,7 +17308,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>616</v>
       </c>
@@ -17560,7 +17560,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
         <v>634</v>
       </c>
@@ -17688,7 +17688,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="118" hidden="true">
+    <row r="118">
       <c r="A118" t="s" s="2">
         <v>645</v>
       </c>
@@ -17816,7 +17816,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="119" hidden="true">
+    <row r="119">
       <c r="A119" t="s" s="2">
         <v>654</v>
       </c>
@@ -17944,7 +17944,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
         <v>662</v>
       </c>
@@ -18070,7 +18070,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="121" hidden="true">
+    <row r="121">
       <c r="A121" t="s" s="2">
         <v>670</v>
       </c>
@@ -18196,7 +18196,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
         <v>678</v>
       </c>
@@ -18570,7 +18570,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="125" hidden="true">
+    <row r="125">
       <c r="A125" t="s" s="2">
         <v>688</v>
       </c>
@@ -18824,7 +18824,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
         <v>690</v>
       </c>
@@ -18950,7 +18950,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="128" hidden="true">
+    <row r="128">
       <c r="A128" t="s" s="2">
         <v>691</v>
       </c>
@@ -19204,7 +19204,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="130" hidden="true">
+    <row r="130">
       <c r="A130" t="s" s="2">
         <v>693</v>
       </c>
@@ -19832,7 +19832,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="135" hidden="true">
+    <row r="135">
       <c r="A135" t="s" s="2">
         <v>710</v>
       </c>
@@ -20584,7 +20584,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
         <v>723</v>
       </c>
@@ -20838,7 +20838,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="143" hidden="true">
+    <row r="143">
       <c r="A143" t="s" s="2">
         <v>725</v>
       </c>
@@ -21346,7 +21346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="147" hidden="true">
+    <row r="147">
       <c r="A147" t="s" s="2">
         <v>729</v>
       </c>
@@ -21720,7 +21720,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="150" hidden="true">
+    <row r="150">
       <c r="A150" t="s" s="2">
         <v>738</v>
       </c>
@@ -21846,7 +21846,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
         <v>747</v>
       </c>
@@ -21974,7 +21974,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152" hidden="true">
+    <row r="152">
       <c r="A152" t="s" s="2">
         <v>756</v>
       </c>
@@ -22346,7 +22346,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="155" hidden="true">
+    <row r="155">
       <c r="A155" t="s" s="2">
         <v>766</v>
       </c>
@@ -22724,7 +22724,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="158" hidden="true">
+    <row r="158">
       <c r="A158" t="s" s="2">
         <v>769</v>
       </c>
@@ -22978,7 +22978,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
         <v>771</v>
       </c>
@@ -23104,7 +23104,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="161" hidden="true">
+    <row r="161">
       <c r="A161" t="s" s="2">
         <v>772</v>
       </c>
@@ -23486,7 +23486,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="164" hidden="true">
+    <row r="164">
       <c r="A164" t="s" s="2">
         <v>775</v>
       </c>
@@ -23862,7 +23862,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="167" hidden="true">
+    <row r="167">
       <c r="A167" t="s" s="2">
         <v>784</v>
       </c>
@@ -24240,7 +24240,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="170" hidden="true">
+    <row r="170">
       <c r="A170" t="s" s="2">
         <v>787</v>
       </c>
@@ -24494,7 +24494,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="172" hidden="true">
+    <row r="172">
       <c r="A172" t="s" s="2">
         <v>789</v>
       </c>
@@ -24620,7 +24620,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="173" hidden="true">
+    <row r="173">
       <c r="A173" t="s" s="2">
         <v>790</v>
       </c>
@@ -25002,7 +25002,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="176" hidden="true">
+    <row r="176">
       <c r="A176" t="s" s="2">
         <v>793</v>
       </c>
@@ -25376,7 +25376,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="179" hidden="true">
+    <row r="179">
       <c r="A179" t="s" s="2">
         <v>800</v>
       </c>
@@ -25628,7 +25628,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="181" hidden="true">
+    <row r="181">
       <c r="A181" t="s" s="2">
         <v>814</v>
       </c>
@@ -25880,7 +25880,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="183" hidden="true">
+    <row r="183">
       <c r="A183" t="s" s="2">
         <v>826</v>
       </c>
@@ -26008,12 +26008,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AR183">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/ig/document/StructureDefinition-medcom-contained-documentreference.xlsx
+++ b/ig/document/StructureDefinition-medcom-contained-documentreference.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7351" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7352" uniqueCount="839">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T10:54:08+00:00</t>
+    <t>2026-04-29T08:07:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -693,6 +693,18 @@
   <si>
     <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-DocumentReference.version}
 </t>
+  </si>
+  <si>
+    <t>R5: An explicitly assigned identifer of a variation of the content in the DocumentReference (new)</t>
+  </si>
+  <si>
+    <t>R5: `DocumentReference.version` (new:string)</t>
+  </si>
+  <si>
+    <t>Element `DocumentReference.version` has a context of DocumentReference based on following the parent source element upwards and mapping to `DocumentReference`.
+Element `DocumentReference.version` has a context of Media based on following the parent source element upwards and mapping to `Media`.
+Element `DocumentReference.version` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).
+While each resource, including the DocumentReference itself, has its own version identifier, this is a formal identifier for the logical version of the DocumentReference as a whole. It would remain constant if the resources were moved to a new server, and all got new individual resource versions, for example.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -5633,12 +5645,14 @@
         <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>219</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>220</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>80</v>
@@ -5696,7 +5710,7 @@
         <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>123</v>
@@ -5728,13 +5742,13 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
         <v>211</v>
       </c>
       <c r="C23" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="D23" t="s" s="2">
         <v>80</v>
@@ -5756,13 +5770,13 @@
         <v>80</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -5854,10 +5868,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5978,10 +5992,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -6102,10 +6116,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -6131,13 +6145,13 @@
         <v>136</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -6145,7 +6159,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>80</v>
@@ -6187,7 +6201,7 @@
         <v>80</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>94</v>
@@ -6228,10 +6242,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -6257,10 +6271,10 @@
         <v>149</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -6299,17 +6313,17 @@
         <v>80</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -6350,13 +6364,13 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C28" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D28" t="s" s="2">
         <v>80</v>
@@ -6381,10 +6395,10 @@
         <v>149</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -6415,25 +6429,25 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>244</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>241</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -6474,10 +6488,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6598,10 +6612,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6724,10 +6738,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6753,16 +6767,16 @@
         <v>136</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>80</v>
@@ -6811,7 +6825,7 @@
         <v>80</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -6835,7 +6849,7 @@
         <v>80</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>80</v>
@@ -6844,7 +6858,7 @@
         <v>80</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>80</v>
@@ -6852,10 +6866,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6881,13 +6895,13 @@
         <v>108</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6937,7 +6951,7 @@
         <v>80</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -6961,7 +6975,7 @@
         <v>80</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>80</v>
@@ -6970,7 +6984,7 @@
         <v>80</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>80</v>
@@ -6978,10 +6992,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -7007,14 +7021,14 @@
         <v>171</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>80</v>
@@ -7063,7 +7077,7 @@
         <v>80</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -7087,7 +7101,7 @@
         <v>80</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>80</v>
@@ -7096,7 +7110,7 @@
         <v>80</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>80</v>
@@ -7104,10 +7118,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -7133,14 +7147,14 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>80</v>
@@ -7189,7 +7203,7 @@
         <v>80</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -7213,7 +7227,7 @@
         <v>80</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>80</v>
@@ -7222,7 +7236,7 @@
         <v>80</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>80</v>
@@ -7230,10 +7244,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -7256,19 +7270,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>80</v>
@@ -7317,7 +7331,7 @@
         <v>80</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -7341,7 +7355,7 @@
         <v>80</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>80</v>
@@ -7350,7 +7364,7 @@
         <v>80</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>80</v>
@@ -7358,10 +7372,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7441,7 +7455,7 @@
         <v>80</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -7482,10 +7496,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7508,19 +7522,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>80</v>
@@ -7569,7 +7583,7 @@
         <v>80</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -7584,36 +7598,36 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="AN37" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AO37" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AP37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AQ37" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AR37" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="AQ37" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AR37" t="s" s="2">
-        <v>300</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7734,10 +7748,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7860,10 +7874,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7889,16 +7903,16 @@
         <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>80</v>
@@ -7908,7 +7922,7 @@
         <v>80</v>
       </c>
       <c r="S40" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="T40" t="s" s="2">
         <v>80</v>
@@ -7926,10 +7940,10 @@
         <v>192</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>80</v>
@@ -7947,7 +7961,7 @@
         <v>80</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -7971,7 +7985,7 @@
         <v>80</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>80</v>
@@ -7988,10 +8002,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -8014,19 +8028,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>80</v>
@@ -8054,10 +8068,10 @@
         <v>153</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>80</v>
@@ -8075,7 +8089,7 @@
         <v>80</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -8099,7 +8113,7 @@
         <v>80</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>80</v>
@@ -8108,7 +8122,7 @@
         <v>80</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>80</v>
@@ -8116,10 +8130,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -8145,16 +8159,16 @@
         <v>136</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>80</v>
@@ -8167,7 +8181,7 @@
         <v>80</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>80</v>
@@ -8203,7 +8217,7 @@
         <v>80</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -8227,7 +8241,7 @@
         <v>80</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>80</v>
@@ -8236,7 +8250,7 @@
         <v>80</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>80</v>
@@ -8244,10 +8258,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -8273,13 +8287,13 @@
         <v>108</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -8293,7 +8307,7 @@
         <v>80</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>80</v>
@@ -8329,7 +8343,7 @@
         <v>80</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -8353,7 +8367,7 @@
         <v>80</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>80</v>
@@ -8362,7 +8376,7 @@
         <v>80</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>80</v>
@@ -8370,10 +8384,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -8396,13 +8410,13 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -8453,7 +8467,7 @@
         <v>80</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -8477,7 +8491,7 @@
         <v>80</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>80</v>
@@ -8486,7 +8500,7 @@
         <v>80</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>80</v>
@@ -8494,10 +8508,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8520,16 +8534,16 @@
         <v>95</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -8579,7 +8593,7 @@
         <v>80</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -8603,7 +8617,7 @@
         <v>80</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>80</v>
@@ -8612,7 +8626,7 @@
         <v>80</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>80</v>
@@ -8620,10 +8634,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8646,13 +8660,13 @@
         <v>95</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -8691,7 +8705,7 @@
         <v>80</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8701,7 +8715,7 @@
         <v>121</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -8716,39 +8730,39 @@
         <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>80</v>
@@ -8770,13 +8784,13 @@
         <v>95</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -8827,7 +8841,7 @@
         <v>80</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8845,33 +8859,33 @@
         <v>80</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AR47" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8992,10 +9006,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -9118,10 +9132,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -9147,16 +9161,16 @@
         <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>80</v>
@@ -9166,7 +9180,7 @@
         <v>80</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="T50" t="s" s="2">
         <v>80</v>
@@ -9184,10 +9198,10 @@
         <v>192</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>80</v>
@@ -9205,7 +9219,7 @@
         <v>80</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -9229,7 +9243,7 @@
         <v>80</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>80</v>
@@ -9246,10 +9260,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -9272,19 +9286,19 @@
         <v>95</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>80</v>
@@ -9312,10 +9326,10 @@
         <v>153</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>80</v>
@@ -9333,7 +9347,7 @@
         <v>80</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -9357,7 +9371,7 @@
         <v>80</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>80</v>
@@ -9366,7 +9380,7 @@
         <v>80</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>80</v>
@@ -9374,10 +9388,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9403,29 +9417,29 @@
         <v>136</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q52" s="2"/>
       <c r="R52" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="S52" t="s" s="2">
         <v>80</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>80</v>
@@ -9461,7 +9475,7 @@
         <v>80</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -9485,7 +9499,7 @@
         <v>80</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>80</v>
@@ -9494,7 +9508,7 @@
         <v>80</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>80</v>
@@ -9502,10 +9516,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9531,13 +9545,13 @@
         <v>108</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9551,7 +9565,7 @@
         <v>80</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>80</v>
@@ -9587,7 +9601,7 @@
         <v>80</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -9599,7 +9613,7 @@
         <v>80</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>80</v>
@@ -9611,7 +9625,7 @@
         <v>80</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>80</v>
@@ -9620,7 +9634,7 @@
         <v>80</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>80</v>
@@ -9628,10 +9642,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9654,13 +9668,13 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -9711,7 +9725,7 @@
         <v>80</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -9735,7 +9749,7 @@
         <v>80</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AO54" t="s" s="2">
         <v>80</v>
@@ -9744,7 +9758,7 @@
         <v>80</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>80</v>
@@ -9752,10 +9766,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9778,16 +9792,16 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9837,7 +9851,7 @@
         <v>80</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9861,7 +9875,7 @@
         <v>80</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>80</v>
@@ -9870,7 +9884,7 @@
         <v>80</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>80</v>
@@ -9878,10 +9892,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9907,13 +9921,13 @@
         <v>171</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9943,7 +9957,7 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>80</v>
@@ -9961,7 +9975,7 @@
         <v>80</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>94</v>
@@ -9976,36 +9990,36 @@
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="AQ56" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AR56" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AQ56" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="AR56" t="s" s="2">
-        <v>397</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -10031,13 +10045,13 @@
         <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -10066,10 +10080,10 @@
         <v>192</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>80</v>
@@ -10087,7 +10101,7 @@
         <v>80</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -10108,19 +10122,19 @@
         <v>80</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>80</v>
@@ -10128,10 +10142,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10154,16 +10168,16 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -10193,7 +10207,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>80</v>
@@ -10211,7 +10225,7 @@
         <v>80</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -10226,36 +10240,36 @@
         <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AR58" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10376,10 +10390,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10502,10 +10516,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10531,16 +10545,16 @@
         <v>149</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>80</v>
@@ -10589,7 +10603,7 @@
         <v>80</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -10613,7 +10627,7 @@
         <v>80</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>80</v>
@@ -10622,7 +10636,7 @@
         <v>80</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>80</v>
@@ -10630,10 +10644,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10754,10 +10768,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10880,10 +10894,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10909,16 +10923,16 @@
         <v>136</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>80</v>
@@ -10967,7 +10981,7 @@
         <v>80</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10991,7 +11005,7 @@
         <v>80</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>80</v>
@@ -11000,7 +11014,7 @@
         <v>80</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>80</v>
@@ -11008,10 +11022,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -11037,13 +11051,13 @@
         <v>108</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -11093,7 +11107,7 @@
         <v>80</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -11117,7 +11131,7 @@
         <v>80</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>80</v>
@@ -11126,7 +11140,7 @@
         <v>80</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>80</v>
@@ -11134,10 +11148,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -11163,14 +11177,14 @@
         <v>171</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>80</v>
@@ -11219,7 +11233,7 @@
         <v>80</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -11243,7 +11257,7 @@
         <v>80</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>80</v>
@@ -11252,7 +11266,7 @@
         <v>80</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>80</v>
@@ -11260,10 +11274,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11289,14 +11303,14 @@
         <v>108</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>80</v>
@@ -11345,7 +11359,7 @@
         <v>80</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -11369,7 +11383,7 @@
         <v>80</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>80</v>
@@ -11378,7 +11392,7 @@
         <v>80</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>80</v>
@@ -11386,10 +11400,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11412,19 +11426,19 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>80</v>
@@ -11473,7 +11487,7 @@
         <v>80</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -11497,7 +11511,7 @@
         <v>80</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>80</v>
@@ -11506,7 +11520,7 @@
         <v>80</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>80</v>
@@ -11514,10 +11528,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11543,16 +11557,16 @@
         <v>108</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>80</v>
@@ -11601,7 +11615,7 @@
         <v>80</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -11625,7 +11639,7 @@
         <v>80</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>80</v>
@@ -11634,7 +11648,7 @@
         <v>80</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>80</v>
@@ -11642,14 +11656,14 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -11668,16 +11682,16 @@
         <v>95</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -11707,7 +11721,7 @@
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>80</v>
@@ -11725,7 +11739,7 @@
         <v>80</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -11740,36 +11754,36 @@
         <v>106</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11890,10 +11904,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -12016,10 +12030,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -12045,16 +12059,16 @@
         <v>149</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>80</v>
@@ -12103,7 +12117,7 @@
         <v>80</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -12127,7 +12141,7 @@
         <v>80</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>80</v>
@@ -12136,7 +12150,7 @@
         <v>80</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>80</v>
@@ -12144,10 +12158,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -12268,10 +12282,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12394,10 +12408,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -12423,16 +12437,16 @@
         <v>136</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>80</v>
@@ -12481,7 +12495,7 @@
         <v>80</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -12505,7 +12519,7 @@
         <v>80</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>80</v>
@@ -12514,7 +12528,7 @@
         <v>80</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>80</v>
@@ -12522,10 +12536,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12551,13 +12565,13 @@
         <v>108</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -12607,7 +12621,7 @@
         <v>80</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -12631,7 +12645,7 @@
         <v>80</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>80</v>
@@ -12640,7 +12654,7 @@
         <v>80</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>80</v>
@@ -12648,10 +12662,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12677,14 +12691,14 @@
         <v>171</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>80</v>
@@ -12733,7 +12747,7 @@
         <v>80</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -12757,7 +12771,7 @@
         <v>80</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>80</v>
@@ -12766,7 +12780,7 @@
         <v>80</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>80</v>
@@ -12774,10 +12788,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12803,14 +12817,14 @@
         <v>108</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>80</v>
@@ -12859,7 +12873,7 @@
         <v>80</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -12883,7 +12897,7 @@
         <v>80</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>80</v>
@@ -12892,7 +12906,7 @@
         <v>80</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>80</v>
@@ -12900,10 +12914,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12926,19 +12940,19 @@
         <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>80</v>
@@ -12987,7 +13001,7 @@
         <v>80</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -13011,7 +13025,7 @@
         <v>80</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>80</v>
@@ -13020,7 +13034,7 @@
         <v>80</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>80</v>
@@ -13028,10 +13042,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -13057,16 +13071,16 @@
         <v>108</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>80</v>
@@ -13115,7 +13129,7 @@
         <v>80</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -13139,7 +13153,7 @@
         <v>80</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>80</v>
@@ -13148,7 +13162,7 @@
         <v>80</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>80</v>
@@ -13156,10 +13170,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13182,13 +13196,13 @@
         <v>95</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -13239,7 +13253,7 @@
         <v>80</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -13254,40 +13268,40 @@
         <v>106</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN82" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AQ82" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="AR82" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AP82" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AQ82" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AR82" t="s" s="2">
-        <v>474</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -13309,13 +13323,13 @@
         <v>130</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -13365,7 +13379,7 @@
         <v>80</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -13383,19 +13397,19 @@
         <v>80</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>80</v>
@@ -13406,10 +13420,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13420,7 +13434,7 @@
         <v>94</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>95</v>
@@ -13432,16 +13446,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13479,7 +13493,7 @@
         <v>80</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AC84" s="2"/>
       <c r="AD84" t="s" s="2">
@@ -13489,7 +13503,7 @@
         <v>121</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -13504,39 +13518,39 @@
         <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AN84" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ84" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AR84" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ84" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AR84" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>80</v>
@@ -13558,16 +13572,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -13617,7 +13631,7 @@
         <v>80</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -13632,36 +13646,36 @@
         <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AN85" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ85" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="AR85" t="s" s="2">
         <v>500</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ85" t="s" s="2">
-        <v>502</v>
-      </c>
-      <c r="AR85" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13684,16 +13698,16 @@
         <v>80</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -13743,7 +13757,7 @@
         <v>80</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -13758,36 +13772,36 @@
         <v>106</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AO86" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AQ86" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="AR86" t="s" s="2">
         <v>515</v>
-      </c>
-      <c r="AP86" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AQ86" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="AR86" t="s" s="2">
-        <v>512</v>
       </c>
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13810,16 +13824,16 @@
         <v>80</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -13869,7 +13883,7 @@
         <v>80</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -13884,16 +13898,16 @@
         <v>106</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>80</v>
@@ -13910,10 +13924,10 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13936,16 +13950,16 @@
         <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -13995,7 +14009,7 @@
         <v>80</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -14010,16 +14024,16 @@
         <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>80</v>
@@ -14031,15 +14045,15 @@
         <v>80</v>
       </c>
       <c r="AR88" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -14160,10 +14174,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14286,14 +14300,14 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
@@ -14315,16 +14329,16 @@
         <v>115</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>80</v>
@@ -14373,7 +14387,7 @@
         <v>80</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -14414,10 +14428,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14443,13 +14457,13 @@
         <v>171</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -14478,10 +14492,10 @@
         <v>192</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>80</v>
@@ -14499,7 +14513,7 @@
         <v>80</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>94</v>
@@ -14514,16 +14528,16 @@
         <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>80</v>
@@ -14535,15 +14549,15 @@
         <v>80</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14566,13 +14580,13 @@
         <v>95</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -14623,7 +14637,7 @@
         <v>80</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>94</v>
@@ -14638,16 +14652,16 @@
         <v>106</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>80</v>
@@ -14659,15 +14673,15 @@
         <v>80</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14693,16 +14707,16 @@
         <v>108</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>80</v>
@@ -14751,7 +14765,7 @@
         <v>80</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -14766,7 +14780,7 @@
         <v>106</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>80</v>
@@ -14775,7 +14789,7 @@
         <v>80</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>80</v>
@@ -14784,18 +14798,18 @@
         <v>80</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="AR94" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -14818,19 +14832,19 @@
         <v>95</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>80</v>
@@ -14879,7 +14893,7 @@
         <v>80</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -14894,36 +14908,36 @@
         <v>106</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="AO95" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AR95" t="s" s="2">
         <v>575</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>572</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -15044,10 +15058,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -15170,10 +15184,10 @@
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15199,16 +15213,16 @@
         <v>149</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>80</v>
@@ -15257,7 +15271,7 @@
         <v>80</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -15281,7 +15295,7 @@
         <v>80</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>80</v>
@@ -15290,7 +15304,7 @@
         <v>80</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>80</v>
@@ -15298,10 +15312,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -15422,10 +15436,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -15548,10 +15562,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -15577,16 +15591,16 @@
         <v>136</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>80</v>
@@ -15635,7 +15649,7 @@
         <v>80</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -15659,7 +15673,7 @@
         <v>80</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>80</v>
@@ -15668,7 +15682,7 @@
         <v>80</v>
       </c>
       <c r="AQ101" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR101" t="s" s="2">
         <v>80</v>
@@ -15676,10 +15690,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -15705,13 +15719,13 @@
         <v>108</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -15761,7 +15775,7 @@
         <v>80</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -15785,7 +15799,7 @@
         <v>80</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>80</v>
@@ -15794,7 +15808,7 @@
         <v>80</v>
       </c>
       <c r="AQ102" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR102" t="s" s="2">
         <v>80</v>
@@ -15802,10 +15816,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -15831,14 +15845,14 @@
         <v>171</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>80</v>
@@ -15887,7 +15901,7 @@
         <v>80</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -15911,7 +15925,7 @@
         <v>80</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>80</v>
@@ -15920,7 +15934,7 @@
         <v>80</v>
       </c>
       <c r="AQ103" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR103" t="s" s="2">
         <v>80</v>
@@ -15928,10 +15942,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -15957,14 +15971,14 @@
         <v>108</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>80</v>
@@ -16013,7 +16027,7 @@
         <v>80</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -16037,7 +16051,7 @@
         <v>80</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>80</v>
@@ -16046,7 +16060,7 @@
         <v>80</v>
       </c>
       <c r="AQ104" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR104" t="s" s="2">
         <v>80</v>
@@ -16054,10 +16068,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -16080,19 +16094,19 @@
         <v>95</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>80</v>
@@ -16141,7 +16155,7 @@
         <v>80</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -16165,7 +16179,7 @@
         <v>80</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>80</v>
@@ -16174,7 +16188,7 @@
         <v>80</v>
       </c>
       <c r="AQ105" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR105" t="s" s="2">
         <v>80</v>
@@ -16182,10 +16196,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -16211,16 +16225,16 @@
         <v>108</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>80</v>
@@ -16269,7 +16283,7 @@
         <v>80</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -16293,7 +16307,7 @@
         <v>80</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>80</v>
@@ -16302,7 +16316,7 @@
         <v>80</v>
       </c>
       <c r="AQ106" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR106" t="s" s="2">
         <v>80</v>
@@ -16310,10 +16324,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -16336,13 +16350,13 @@
         <v>95</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -16393,7 +16407,7 @@
         <v>80</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>94</v>
@@ -16414,10 +16428,10 @@
         <v>80</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>80</v>
@@ -16434,10 +16448,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -16558,10 +16572,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -16684,14 +16698,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -16713,16 +16727,16 @@
         <v>115</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="N110" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>80</v>
@@ -16771,7 +16785,7 @@
         <v>80</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -16812,10 +16826,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -16838,13 +16852,13 @@
         <v>95</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -16895,7 +16909,7 @@
         <v>80</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>94</v>
@@ -16916,30 +16930,30 @@
         <v>80</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AO111" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AP111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AQ111" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AR111" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -17060,10 +17074,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -17186,10 +17200,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -17215,14 +17229,14 @@
         <v>171</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>80</v>
@@ -17235,7 +17249,7 @@
         <v>80</v>
       </c>
       <c r="T114" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="U114" t="s" s="2">
         <v>80</v>
@@ -17251,7 +17265,7 @@
       </c>
       <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>80</v>
@@ -17269,7 +17283,7 @@
         <v>80</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -17284,7 +17298,7 @@
         <v>106</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AL114" t="s" s="2">
         <v>80</v>
@@ -17293,7 +17307,7 @@
         <v>80</v>
       </c>
       <c r="AN114" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AO114" t="s" s="2">
         <v>80</v>
@@ -17302,7 +17316,7 @@
         <v>80</v>
       </c>
       <c r="AQ114" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="AR114" t="s" s="2">
         <v>80</v>
@@ -17310,10 +17324,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -17339,14 +17353,14 @@
         <v>171</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>80</v>
@@ -17359,7 +17373,7 @@
         <v>80</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>80</v>
@@ -17375,7 +17389,7 @@
       </c>
       <c r="Y115" s="2"/>
       <c r="Z115" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>80</v>
@@ -17393,7 +17407,7 @@
         <v>80</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -17408,7 +17422,7 @@
         <v>106</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AL115" t="s" s="2">
         <v>80</v>
@@ -17417,7 +17431,7 @@
         <v>80</v>
       </c>
       <c r="AN115" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AO115" t="s" s="2">
         <v>80</v>
@@ -17434,10 +17448,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -17460,19 +17474,19 @@
         <v>80</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>80</v>
@@ -17521,7 +17535,7 @@
         <v>80</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -17545,7 +17559,7 @@
         <v>80</v>
       </c>
       <c r="AN116" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="AO116" t="s" s="2">
         <v>80</v>
@@ -17554,7 +17568,7 @@
         <v>80</v>
       </c>
       <c r="AQ116" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AR116" t="s" s="2">
         <v>80</v>
@@ -17562,10 +17576,10 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -17588,19 +17602,19 @@
         <v>95</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="O117" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>80</v>
@@ -17613,7 +17627,7 @@
         <v>80</v>
       </c>
       <c r="T117" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="U117" t="s" s="2">
         <v>80</v>
@@ -17649,7 +17663,7 @@
         <v>80</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -17664,7 +17678,7 @@
         <v>106</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="AL117" t="s" s="2">
         <v>80</v>
@@ -17673,7 +17687,7 @@
         <v>80</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="AO117" t="s" s="2">
         <v>80</v>
@@ -17682,7 +17696,7 @@
         <v>80</v>
       </c>
       <c r="AQ117" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="AR117" t="s" s="2">
         <v>80</v>
@@ -17690,10 +17704,10 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -17716,19 +17730,19 @@
         <v>95</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>80</v>
@@ -17777,7 +17791,7 @@
         <v>80</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -17792,7 +17806,7 @@
         <v>106</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AL118" t="s" s="2">
         <v>80</v>
@@ -17801,7 +17815,7 @@
         <v>80</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AO118" t="s" s="2">
         <v>80</v>
@@ -17818,10 +17832,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -17844,19 +17858,19 @@
         <v>95</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>80</v>
@@ -17905,7 +17919,7 @@
         <v>80</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -17920,7 +17934,7 @@
         <v>106</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="AL119" t="s" s="2">
         <v>80</v>
@@ -17929,7 +17943,7 @@
         <v>80</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AO119" t="s" s="2">
         <v>80</v>
@@ -17946,10 +17960,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -17975,14 +17989,14 @@
         <v>108</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>80</v>
@@ -17995,7 +18009,7 @@
         <v>80</v>
       </c>
       <c r="T120" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="U120" t="s" s="2">
         <v>80</v>
@@ -18031,7 +18045,7 @@
         <v>80</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -18046,7 +18060,7 @@
         <v>106</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AL120" t="s" s="2">
         <v>80</v>
@@ -18055,7 +18069,7 @@
         <v>80</v>
       </c>
       <c r="AN120" t="s" s="2">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="AO120" t="s" s="2">
         <v>80</v>
@@ -18072,10 +18086,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -18098,17 +18112,17 @@
         <v>95</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>80</v>
@@ -18157,7 +18171,7 @@
         <v>80</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -18169,10 +18183,10 @@
         <v>80</v>
       </c>
       <c r="AJ121" t="s" s="2">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>80</v>
@@ -18181,7 +18195,7 @@
         <v>80</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="AO121" t="s" s="2">
         <v>80</v>
@@ -18198,10 +18212,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -18227,13 +18241,13 @@
         <v>149</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>679</v>
+        <v>682</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>680</v>
+        <v>683</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -18263,7 +18277,7 @@
       </c>
       <c r="Y122" s="2"/>
       <c r="Z122" t="s" s="2">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>80</v>
@@ -18281,7 +18295,7 @@
         <v>80</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>81</v>
@@ -18296,19 +18310,19 @@
         <v>106</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="AL122" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="AN122" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="AO122" t="s" s="2">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="AP122" t="s" s="2">
         <v>80</v>
@@ -18317,15 +18331,15 @@
         <v>80</v>
       </c>
       <c r="AR122" t="s" s="2">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -18446,10 +18460,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -18572,10 +18586,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -18601,16 +18615,16 @@
         <v>136</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>80</v>
@@ -18659,7 +18673,7 @@
         <v>80</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
@@ -18683,7 +18697,7 @@
         <v>80</v>
       </c>
       <c r="AN125" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO125" t="s" s="2">
         <v>80</v>
@@ -18692,7 +18706,7 @@
         <v>80</v>
       </c>
       <c r="AQ125" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR125" t="s" s="2">
         <v>80</v>
@@ -18700,10 +18714,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -18729,13 +18743,13 @@
         <v>108</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -18785,7 +18799,7 @@
         <v>80</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
@@ -18809,7 +18823,7 @@
         <v>80</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO126" t="s" s="2">
         <v>80</v>
@@ -18818,7 +18832,7 @@
         <v>80</v>
       </c>
       <c r="AQ126" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR126" t="s" s="2">
         <v>80</v>
@@ -18826,10 +18840,10 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -18855,14 +18869,14 @@
         <v>171</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>80</v>
@@ -18911,7 +18925,7 @@
         <v>80</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -18935,7 +18949,7 @@
         <v>80</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO127" t="s" s="2">
         <v>80</v>
@@ -18944,7 +18958,7 @@
         <v>80</v>
       </c>
       <c r="AQ127" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR127" t="s" s="2">
         <v>80</v>
@@ -18952,10 +18966,10 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>691</v>
+        <v>694</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -18981,14 +18995,14 @@
         <v>108</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>80</v>
@@ -19037,7 +19051,7 @@
         <v>80</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -19061,7 +19075,7 @@
         <v>80</v>
       </c>
       <c r="AN128" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO128" t="s" s="2">
         <v>80</v>
@@ -19070,7 +19084,7 @@
         <v>80</v>
       </c>
       <c r="AQ128" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR128" t="s" s="2">
         <v>80</v>
@@ -19078,10 +19092,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -19104,19 +19118,19 @@
         <v>95</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>80</v>
@@ -19165,7 +19179,7 @@
         <v>80</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -19189,7 +19203,7 @@
         <v>80</v>
       </c>
       <c r="AN129" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO129" t="s" s="2">
         <v>80</v>
@@ -19198,7 +19212,7 @@
         <v>80</v>
       </c>
       <c r="AQ129" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR129" t="s" s="2">
         <v>80</v>
@@ -19206,10 +19220,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -19232,16 +19246,16 @@
         <v>95</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>695</v>
+        <v>698</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
@@ -19291,7 +19305,7 @@
         <v>80</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -19315,7 +19329,7 @@
         <v>80</v>
       </c>
       <c r="AN130" t="s" s="2">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="AO130" t="s" s="2">
         <v>80</v>
@@ -19332,10 +19346,10 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -19456,10 +19470,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -19582,14 +19596,14 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>700</v>
+        <v>703</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="E133" s="2"/>
       <c r="F133" t="s" s="2">
@@ -19611,16 +19625,16 @@
         <v>115</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="N133" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>80</v>
@@ -19669,7 +19683,7 @@
         <v>80</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
@@ -19710,10 +19724,10 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -19736,13 +19750,13 @@
         <v>80</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -19793,7 +19807,7 @@
         <v>80</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
@@ -19808,22 +19822,22 @@
         <v>106</v>
       </c>
       <c r="AK134" t="s" s="2">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="AL134" t="s" s="2">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="AN134" t="s" s="2">
-        <v>708</v>
+        <v>711</v>
       </c>
       <c r="AO134" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AP134" t="s" s="2">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="AQ134" t="s" s="2">
         <v>80</v>
@@ -19834,10 +19848,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -19860,16 +19874,16 @@
         <v>80</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
@@ -19899,7 +19913,7 @@
       </c>
       <c r="Y135" s="2"/>
       <c r="Z135" t="s" s="2">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>80</v>
@@ -19917,7 +19931,7 @@
         <v>80</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -19932,16 +19946,16 @@
         <v>106</v>
       </c>
       <c r="AK135" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="AL135" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>716</v>
+        <v>719</v>
       </c>
       <c r="AN135" t="s" s="2">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="AO135" t="s" s="2">
         <v>80</v>
@@ -19953,15 +19967,15 @@
         <v>80</v>
       </c>
       <c r="AR135" t="s" s="2">
-        <v>715</v>
+        <v>718</v>
       </c>
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -20082,10 +20096,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -20208,10 +20222,10 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>720</v>
+        <v>723</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -20237,16 +20251,16 @@
         <v>149</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O138" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>80</v>
@@ -20295,7 +20309,7 @@
         <v>80</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
@@ -20319,7 +20333,7 @@
         <v>80</v>
       </c>
       <c r="AN138" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO138" t="s" s="2">
         <v>80</v>
@@ -20328,7 +20342,7 @@
         <v>80</v>
       </c>
       <c r="AQ138" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR138" t="s" s="2">
         <v>80</v>
@@ -20336,10 +20350,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -20460,10 +20474,10 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -20586,10 +20600,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -20615,16 +20629,16 @@
         <v>136</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O141" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P141" t="s" s="2">
         <v>80</v>
@@ -20673,7 +20687,7 @@
         <v>80</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -20697,7 +20711,7 @@
         <v>80</v>
       </c>
       <c r="AN141" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO141" t="s" s="2">
         <v>80</v>
@@ -20706,7 +20720,7 @@
         <v>80</v>
       </c>
       <c r="AQ141" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR141" t="s" s="2">
         <v>80</v>
@@ -20714,10 +20728,10 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>724</v>
+        <v>727</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -20743,13 +20757,13 @@
         <v>108</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N142" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O142" s="2"/>
       <c r="P142" t="s" s="2">
@@ -20799,7 +20813,7 @@
         <v>80</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -20823,7 +20837,7 @@
         <v>80</v>
       </c>
       <c r="AN142" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO142" t="s" s="2">
         <v>80</v>
@@ -20832,7 +20846,7 @@
         <v>80</v>
       </c>
       <c r="AQ142" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR142" t="s" s="2">
         <v>80</v>
@@ -20840,10 +20854,10 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
@@ -20869,14 +20883,14 @@
         <v>171</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P143" t="s" s="2">
         <v>80</v>
@@ -20925,7 +20939,7 @@
         <v>80</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -20949,7 +20963,7 @@
         <v>80</v>
       </c>
       <c r="AN143" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO143" t="s" s="2">
         <v>80</v>
@@ -20958,7 +20972,7 @@
         <v>80</v>
       </c>
       <c r="AQ143" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR143" t="s" s="2">
         <v>80</v>
@@ -20966,10 +20980,10 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
@@ -20995,14 +21009,14 @@
         <v>108</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N144" s="2"/>
       <c r="O144" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>80</v>
@@ -21051,7 +21065,7 @@
         <v>80</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>81</v>
@@ -21075,7 +21089,7 @@
         <v>80</v>
       </c>
       <c r="AN144" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO144" t="s" s="2">
         <v>80</v>
@@ -21084,7 +21098,7 @@
         <v>80</v>
       </c>
       <c r="AQ144" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR144" t="s" s="2">
         <v>80</v>
@@ -21092,10 +21106,10 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -21118,19 +21132,19 @@
         <v>95</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>80</v>
@@ -21179,7 +21193,7 @@
         <v>80</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -21203,7 +21217,7 @@
         <v>80</v>
       </c>
       <c r="AN145" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO145" t="s" s="2">
         <v>80</v>
@@ -21212,7 +21226,7 @@
         <v>80</v>
       </c>
       <c r="AQ145" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR145" t="s" s="2">
         <v>80</v>
@@ -21220,10 +21234,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>728</v>
+        <v>731</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -21249,16 +21263,16 @@
         <v>108</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O146" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>80</v>
@@ -21307,7 +21321,7 @@
         <v>80</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>81</v>
@@ -21331,7 +21345,7 @@
         <v>80</v>
       </c>
       <c r="AN146" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO146" t="s" s="2">
         <v>80</v>
@@ -21340,7 +21354,7 @@
         <v>80</v>
       </c>
       <c r="AQ146" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR146" t="s" s="2">
         <v>80</v>
@@ -21348,10 +21362,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -21374,13 +21388,13 @@
         <v>95</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
@@ -21431,7 +21445,7 @@
         <v>80</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -21452,13 +21466,13 @@
         <v>80</v>
       </c>
       <c r="AM147" t="s" s="2">
-        <v>732</v>
+        <v>735</v>
       </c>
       <c r="AN147" t="s" s="2">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="AO147" t="s" s="2">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="AP147" t="s" s="2">
         <v>80</v>
@@ -21467,15 +21481,15 @@
         <v>80</v>
       </c>
       <c r="AR147" t="s" s="2">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -21596,10 +21610,10 @@
     </row>
     <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -21722,10 +21736,10 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
@@ -21748,16 +21762,16 @@
         <v>95</v>
       </c>
       <c r="K150" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>741</v>
+        <v>744</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -21807,7 +21821,7 @@
         <v>80</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -21816,13 +21830,13 @@
         <v>94</v>
       </c>
       <c r="AI150" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AJ150" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK150" t="s" s="2">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="AL150" t="s" s="2">
         <v>80</v>
@@ -21831,7 +21845,7 @@
         <v>80</v>
       </c>
       <c r="AN150" t="s" s="2">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="AO150" t="s" s="2">
         <v>80</v>
@@ -21840,7 +21854,7 @@
         <v>80</v>
       </c>
       <c r="AQ150" t="s" s="2">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AR150" t="s" s="2">
         <v>80</v>
@@ -21848,10 +21862,10 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>747</v>
+        <v>750</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
@@ -21874,23 +21888,23 @@
         <v>95</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>750</v>
+        <v>753</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" t="s" s="2">
         <v>80</v>
       </c>
       <c r="Q151" t="s" s="2">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="R151" t="s" s="2">
         <v>80</v>
@@ -21935,7 +21949,7 @@
         <v>80</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -21944,13 +21958,13 @@
         <v>94</v>
       </c>
       <c r="AI151" t="s" s="2">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="AJ151" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK151" t="s" s="2">
-        <v>753</v>
+        <v>756</v>
       </c>
       <c r="AL151" t="s" s="2">
         <v>80</v>
@@ -21959,7 +21973,7 @@
         <v>80</v>
       </c>
       <c r="AN151" t="s" s="2">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="AO151" t="s" s="2">
         <v>80</v>
@@ -21968,7 +21982,7 @@
         <v>80</v>
       </c>
       <c r="AQ151" t="s" s="2">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="AR151" t="s" s="2">
         <v>80</v>
@@ -21976,10 +21990,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -22002,13 +22016,13 @@
         <v>80</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>757</v>
+        <v>760</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
@@ -22039,25 +22053,25 @@
       </c>
       <c r="Y152" s="2"/>
       <c r="Z152" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="AA152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AB152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AC152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AD152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AE152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AF152" t="s" s="2">
         <v>759</v>
-      </c>
-      <c r="AA152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AB152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AC152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AD152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AE152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AF152" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -22072,36 +22086,36 @@
         <v>106</v>
       </c>
       <c r="AK152" t="s" s="2">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="AL152" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM152" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AN152" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AO152" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="AP152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AQ152" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AR152" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="AP152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AQ152" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AR152" t="s" s="2">
-        <v>760</v>
       </c>
     </row>
     <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -22222,10 +22236,10 @@
     </row>
     <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -22348,10 +22362,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -22377,16 +22391,16 @@
         <v>149</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>80</v>
@@ -22435,7 +22449,7 @@
         <v>80</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -22459,7 +22473,7 @@
         <v>80</v>
       </c>
       <c r="AN155" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO155" t="s" s="2">
         <v>80</v>
@@ -22468,7 +22482,7 @@
         <v>80</v>
       </c>
       <c r="AQ155" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR155" t="s" s="2">
         <v>80</v>
@@ -22476,10 +22490,10 @@
     </row>
     <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
@@ -22600,10 +22614,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -22726,10 +22740,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>769</v>
+        <v>772</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -22755,16 +22769,16 @@
         <v>136</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>80</v>
@@ -22813,7 +22827,7 @@
         <v>80</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>81</v>
@@ -22837,7 +22851,7 @@
         <v>80</v>
       </c>
       <c r="AN158" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO158" t="s" s="2">
         <v>80</v>
@@ -22846,7 +22860,7 @@
         <v>80</v>
       </c>
       <c r="AQ158" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR158" t="s" s="2">
         <v>80</v>
@@ -22854,10 +22868,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -22883,13 +22897,13 @@
         <v>108</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O159" s="2"/>
       <c r="P159" t="s" s="2">
@@ -22939,7 +22953,7 @@
         <v>80</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -22963,7 +22977,7 @@
         <v>80</v>
       </c>
       <c r="AN159" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO159" t="s" s="2">
         <v>80</v>
@@ -22972,7 +22986,7 @@
         <v>80</v>
       </c>
       <c r="AQ159" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR159" t="s" s="2">
         <v>80</v>
@@ -22980,10 +22994,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -23009,14 +23023,14 @@
         <v>171</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>80</v>
@@ -23065,7 +23079,7 @@
         <v>80</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -23089,7 +23103,7 @@
         <v>80</v>
       </c>
       <c r="AN160" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO160" t="s" s="2">
         <v>80</v>
@@ -23098,7 +23112,7 @@
         <v>80</v>
       </c>
       <c r="AQ160" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR160" t="s" s="2">
         <v>80</v>
@@ -23106,10 +23120,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -23135,14 +23149,14 @@
         <v>108</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>80</v>
@@ -23191,7 +23205,7 @@
         <v>80</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
@@ -23215,7 +23229,7 @@
         <v>80</v>
       </c>
       <c r="AN161" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO161" t="s" s="2">
         <v>80</v>
@@ -23224,7 +23238,7 @@
         <v>80</v>
       </c>
       <c r="AQ161" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR161" t="s" s="2">
         <v>80</v>
@@ -23232,10 +23246,10 @@
     </row>
     <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>773</v>
+        <v>776</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -23258,19 +23272,19 @@
         <v>95</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N162" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O162" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>80</v>
@@ -23319,7 +23333,7 @@
         <v>80</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -23343,7 +23357,7 @@
         <v>80</v>
       </c>
       <c r="AN162" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO162" t="s" s="2">
         <v>80</v>
@@ -23352,7 +23366,7 @@
         <v>80</v>
       </c>
       <c r="AQ162" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR162" t="s" s="2">
         <v>80</v>
@@ -23360,10 +23374,10 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -23389,16 +23403,16 @@
         <v>108</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>80</v>
@@ -23447,7 +23461,7 @@
         <v>80</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -23471,7 +23485,7 @@
         <v>80</v>
       </c>
       <c r="AN163" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO163" t="s" s="2">
         <v>80</v>
@@ -23480,7 +23494,7 @@
         <v>80</v>
       </c>
       <c r="AQ163" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR163" t="s" s="2">
         <v>80</v>
@@ -23488,10 +23502,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -23514,19 +23528,19 @@
         <v>80</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>777</v>
+        <v>780</v>
       </c>
       <c r="N164" t="s" s="2">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="O164" t="s" s="2">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>80</v>
@@ -23555,7 +23569,7 @@
       </c>
       <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>80</v>
@@ -23573,7 +23587,7 @@
         <v>80</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
@@ -23588,19 +23602,19 @@
         <v>106</v>
       </c>
       <c r="AK164" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
       <c r="AL164" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM164" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AN164" t="s" s="2">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="AO164" t="s" s="2">
-        <v>761</v>
+        <v>764</v>
       </c>
       <c r="AP164" t="s" s="2">
         <v>80</v>
@@ -23609,15 +23623,15 @@
         <v>80</v>
       </c>
       <c r="AR164" t="s" s="2">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -23738,10 +23752,10 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -23864,10 +23878,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -23893,16 +23907,16 @@
         <v>149</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N167" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="O167" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>80</v>
@@ -23951,7 +23965,7 @@
         <v>80</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -23975,7 +23989,7 @@
         <v>80</v>
       </c>
       <c r="AN167" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AO167" t="s" s="2">
         <v>80</v>
@@ -23984,7 +23998,7 @@
         <v>80</v>
       </c>
       <c r="AQ167" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR167" t="s" s="2">
         <v>80</v>
@@ -23992,10 +24006,10 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -24116,10 +24130,10 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
@@ -24242,10 +24256,10 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
@@ -24271,16 +24285,16 @@
         <v>136</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>80</v>
@@ -24329,7 +24343,7 @@
         <v>80</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -24353,7 +24367,7 @@
         <v>80</v>
       </c>
       <c r="AN170" t="s" s="2">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="AO170" t="s" s="2">
         <v>80</v>
@@ -24362,7 +24376,7 @@
         <v>80</v>
       </c>
       <c r="AQ170" t="s" s="2">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="AR170" t="s" s="2">
         <v>80</v>
@@ -24370,10 +24384,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -24399,13 +24413,13 @@
         <v>108</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="N171" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -24455,7 +24469,7 @@
         <v>80</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
@@ -24479,7 +24493,7 @@
         <v>80</v>
       </c>
       <c r="AN171" t="s" s="2">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="AO171" t="s" s="2">
         <v>80</v>
@@ -24488,7 +24502,7 @@
         <v>80</v>
       </c>
       <c r="AQ171" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AR171" t="s" s="2">
         <v>80</v>
@@ -24496,10 +24510,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>789</v>
+        <v>792</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -24525,14 +24539,14 @@
         <v>171</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>80</v>
@@ -24581,7 +24595,7 @@
         <v>80</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -24605,7 +24619,7 @@
         <v>80</v>
       </c>
       <c r="AN172" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="AO172" t="s" s="2">
         <v>80</v>
@@ -24614,7 +24628,7 @@
         <v>80</v>
       </c>
       <c r="AQ172" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AR172" t="s" s="2">
         <v>80</v>
@@ -24622,10 +24636,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -24651,14 +24665,14 @@
         <v>108</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>80</v>
@@ -24707,7 +24721,7 @@
         <v>80</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -24731,7 +24745,7 @@
         <v>80</v>
       </c>
       <c r="AN173" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="AO173" t="s" s="2">
         <v>80</v>
@@ -24740,7 +24754,7 @@
         <v>80</v>
       </c>
       <c r="AQ173" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="AR173" t="s" s="2">
         <v>80</v>
@@ -24748,10 +24762,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -24774,19 +24788,19 @@
         <v>95</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>80</v>
@@ -24835,7 +24849,7 @@
         <v>80</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -24859,7 +24873,7 @@
         <v>80</v>
       </c>
       <c r="AN174" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AO174" t="s" s="2">
         <v>80</v>
@@ -24868,7 +24882,7 @@
         <v>80</v>
       </c>
       <c r="AQ174" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AR174" t="s" s="2">
         <v>80</v>
@@ -24876,10 +24890,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -24905,16 +24919,16 @@
         <v>108</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>80</v>
@@ -24963,7 +24977,7 @@
         <v>80</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -24987,7 +25001,7 @@
         <v>80</v>
       </c>
       <c r="AN175" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO175" t="s" s="2">
         <v>80</v>
@@ -24996,7 +25010,7 @@
         <v>80</v>
       </c>
       <c r="AQ175" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="AR175" t="s" s="2">
         <v>80</v>
@@ -25004,10 +25018,10 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -25030,13 +25044,13 @@
         <v>80</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -25087,7 +25101,7 @@
         <v>80</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>793</v>
+        <v>796</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -25108,13 +25122,13 @@
         <v>80</v>
       </c>
       <c r="AM176" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AN176" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AO176" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AP176" t="s" s="2">
         <v>80</v>
@@ -25123,15 +25137,15 @@
         <v>80</v>
       </c>
       <c r="AR176" t="s" s="2">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -25252,10 +25266,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -25378,10 +25392,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -25407,13 +25421,13 @@
         <v>108</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="N179" t="s" s="2">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="O179" s="2"/>
       <c r="P179" t="s" s="2">
@@ -25463,7 +25477,7 @@
         <v>80</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -25472,13 +25486,13 @@
         <v>94</v>
       </c>
       <c r="AI179" t="s" s="2">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="AJ179" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK179" t="s" s="2">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="AL179" t="s" s="2">
         <v>80</v>
@@ -25504,10 +25518,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -25533,13 +25547,13 @@
         <v>136</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>809</v>
+        <v>812</v>
       </c>
       <c r="N180" t="s" s="2">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="O180" s="2"/>
       <c r="P180" t="s" s="2">
@@ -25568,10 +25582,10 @@
         <v>153</v>
       </c>
       <c r="Y180" t="s" s="2">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="Z180" t="s" s="2">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="AA180" t="s" s="2">
         <v>80</v>
@@ -25589,7 +25603,7 @@
         <v>80</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>813</v>
+        <v>816</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -25630,10 +25644,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -25656,16 +25670,16 @@
         <v>95</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="N181" t="s" s="2">
-        <v>817</v>
+        <v>820</v>
       </c>
       <c r="O181" s="2"/>
       <c r="P181" t="s" s="2">
@@ -25715,7 +25729,7 @@
         <v>80</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -25730,7 +25744,7 @@
         <v>106</v>
       </c>
       <c r="AK181" t="s" s="2">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="AL181" t="s" s="2">
         <v>80</v>
@@ -25739,7 +25753,7 @@
         <v>80</v>
       </c>
       <c r="AN181" t="s" s="2">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="AO181" t="s" s="2">
         <v>80</v>
@@ -25756,10 +25770,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>821</v>
+        <v>824</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -25785,13 +25799,13 @@
         <v>108</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="O182" s="2"/>
       <c r="P182" t="s" s="2">
@@ -25841,7 +25855,7 @@
         <v>80</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>825</v>
+        <v>828</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -25882,10 +25896,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -25908,16 +25922,16 @@
         <v>80</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>829</v>
+        <v>832</v>
       </c>
       <c r="N183" t="s" s="2">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="O183" s="2"/>
       <c r="P183" t="s" s="2">
@@ -25967,7 +25981,7 @@
         <v>80</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -25982,19 +25996,19 @@
         <v>106</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="AL183" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AM183" t="s" s="2">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="AN183" t="s" s="2">
-        <v>833</v>
+        <v>836</v>
       </c>
       <c r="AO183" t="s" s="2">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="AP183" t="s" s="2">
         <v>80</v>
@@ -26003,7 +26017,7 @@
         <v>80</v>
       </c>
       <c r="AR183" t="s" s="2">
-        <v>835</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
